--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484681_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484681_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C. HORTELANO ESCRIBA</t>
+          <t>M. GONZALEZ BRU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,58 +565,58 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4169</v>
+        <v>1.3108</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1148</v>
+        <v>1.3844</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6979</v>
+        <v>-0.0736</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.7785</v>
+        <v>-0.533</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.6116</v>
+        <v>0.4192</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.1669</v>
+        <v>-0.9520999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>3.262</v>
+        <v>1.2088</v>
       </c>
       <c r="K2" t="n">
-        <v>2.5694</v>
+        <v>1.8082</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6925</v>
+        <v>-0.5994</v>
       </c>
       <c r="M2" t="n">
-        <v>-5.0404</v>
+        <v>-1.7418</v>
       </c>
       <c r="N2" t="n">
-        <v>-3.181</v>
+        <v>-1.389</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.8594</v>
+        <v>-0.3528</v>
       </c>
       <c r="P2" t="n">
-        <v>1.6493</v>
+        <v>1.4661</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.5656</v>
+        <v>1.4661</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9022</v>
+        <v>-0.2662</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1252</v>
+        <v>-0.4683</v>
       </c>
       <c r="U2" t="n">
-        <v>0.777</v>
+        <v>0.2021</v>
       </c>
       <c r="V2" t="n">
         <v>0.6439</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. GONZALEZ BRU</t>
+          <t>C. HORTELANO ESCRIBA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0634</v>
+        <v>0.6281</v>
       </c>
       <c r="E3" t="n">
-        <v>1.137</v>
+        <v>2.648</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0736</v>
+        <v>-2.0199</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.533</v>
+        <v>-1.7785</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4192</v>
+        <v>-0.6116</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9520999999999999</v>
+        <v>-1.1669</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2088</v>
+        <v>3.262</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8082</v>
+        <v>2.5694</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5994</v>
+        <v>0.6925</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.7418</v>
+        <v>-5.0404</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.389</v>
+        <v>-3.181</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3528</v>
+        <v>-1.8594</v>
       </c>
       <c r="P3" t="n">
-        <v>1.4661</v>
+        <v>1.6493</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4661</v>
+        <v>2.5656</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5135999999999999</v>
+        <v>0.1133</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7157</v>
+        <v>-0.3416</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2021</v>
+        <v>0.4549</v>
       </c>
       <c r="V3" t="n">
         <v>0.6439</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.3718</v>
+        <v>-0.8386</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.7278</v>
+        <v>-1.3432</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3559</v>
+        <v>0.5046</v>
       </c>
       <c r="G4" t="n">
         <v>-0.5727</v>
@@ -766,13 +766,13 @@
         <v>0.5498</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4326</v>
+        <v>0.1007</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2572</v>
+        <v>0.1275</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1754</v>
+        <v>-0.0268</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.5123</v>
+        <v>-0.9432</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.338</v>
+        <v>-0.8433</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1742</v>
+        <v>-0.0999</v>
       </c>
       <c r="G5" t="n">
         <v>-1.3492</v>
@@ -844,13 +844,13 @@
         <v>2.1991</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1239</v>
+        <v>-0.5548999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7534</v>
+        <v>-0.2586</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3705</v>
+        <v>-0.2962</v>
       </c>
       <c r="V5" t="n">
         <v>-0.3219</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. CISNEROS RUIZ</t>
+          <t>S. CABRERA GONZALEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.2505</v>
+        <v>-2.1727</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.0494</v>
+        <v>-1.0805</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7989000000000001</v>
+        <v>-1.0922</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.9147</v>
+        <v>-0.8173</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.4757</v>
+        <v>-1.7662</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.439</v>
+        <v>0.949</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.1422</v>
+        <v>-1.1438</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.511</v>
+        <v>-1.1954</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6312</v>
+        <v>0.0515</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7726</v>
+        <v>0.3265</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9647</v>
+        <v>-0.5709</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1922</v>
+        <v>0.8974</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3665</v>
+        <v>0.733</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4661</v>
+        <v>0.733</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0307</v>
+        <v>-0.188</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0746</v>
+        <v>0.0634</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1053</v>
+        <v>-0.2513</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.9005</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.9005</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. CABRERA GONZALEZ</t>
+          <t>M. CISNEROS RUIZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.4889</v>
+        <v>-2.2173</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2728</v>
+        <v>-3.0905</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2161</v>
+        <v>0.8732</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8173</v>
+        <v>-1.9147</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.7662</v>
+        <v>-1.4757</v>
       </c>
       <c r="I7" t="n">
-        <v>0.949</v>
+        <v>-0.439</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.1438</v>
+        <v>-1.1422</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.1954</v>
+        <v>-0.511</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0515</v>
+        <v>-0.6312</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3265</v>
+        <v>-0.7726</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5709</v>
+        <v>-0.9647</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8974</v>
+        <v>0.1922</v>
       </c>
       <c r="P7" t="n">
-        <v>0.733</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R7" t="n">
-        <v>0.733</v>
+        <v>1.4661</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5041</v>
+        <v>0.0639</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.129</v>
+        <v>-0.1157</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3752</v>
+        <v>0.1797</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.9005</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.9005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.8793</v>
+        <v>-4.6538</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9442</v>
+        <v>-1.793</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.9351</v>
+        <v>-2.8608</v>
       </c>
       <c r="G8" t="n">
         <v>-5.0563</v>
@@ -1078,13 +1078,13 @@
         <v>1.4661</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9776</v>
+        <v>-0.7521</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5332</v>
+        <v>-0.382</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4444</v>
+        <v>-0.3701</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3115</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. SOLBES SORIANO</t>
+          <t>S. CARRION BALLESTER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.4084</v>
+        <v>-5.5259</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7078</v>
+        <v>-4.0514</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.7006</v>
+        <v>-1.4745</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.3327</v>
+        <v>-3.5287</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.358</v>
+        <v>-0.1121</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9747</v>
+        <v>-3.4167</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.753</v>
+        <v>-0.0376</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.8364</v>
+        <v>1.8082</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0833</v>
+        <v>-1.8458</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.5796</v>
+        <v>-3.4911</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.5216</v>
+        <v>-1.9202</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0581</v>
+        <v>-1.5709</v>
       </c>
       <c r="P9" t="n">
-        <v>0.733</v>
+        <v>-2.0158</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9163</v>
+        <v>-3.6651</v>
       </c>
       <c r="R9" t="n">
         <v>1.6493</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4868</v>
+        <v>0.0083</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0384</v>
+        <v>-0.0475</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4483</v>
+        <v>0.0558</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3219</v>
+        <v>0.0104</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.3011</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3219</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. CARRION BALLESTER</t>
+          <t>A. SOLBES SORIANO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.4877</v>
+        <v>-5.573</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.9141</v>
+        <v>-2.9962</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5736</v>
+        <v>-2.5768</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.5287</v>
+        <v>-5.3327</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1121</v>
+        <v>-4.358</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.4167</v>
+        <v>-0.9747</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0376</v>
+        <v>-1.753</v>
       </c>
       <c r="K10" t="n">
-        <v>1.8082</v>
+        <v>-1.8364</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.8458</v>
+        <v>0.0833</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.4911</v>
+        <v>-3.5796</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.9202</v>
+        <v>-2.5216</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.5709</v>
+        <v>-1.0581</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.0158</v>
+        <v>0.733</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.6651</v>
+        <v>-0.9163</v>
       </c>
       <c r="R10" t="n">
         <v>1.6493</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0465</v>
+        <v>-0.6514</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0898</v>
+        <v>-0.3269</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0433</v>
+        <v>-0.3245</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0104</v>
+        <v>-0.3219</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3011</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3115</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.8339</v>
+        <v>-6.3235</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.672</v>
+        <v>-4.8644</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1619</v>
+        <v>-1.4592</v>
       </c>
       <c r="G11" t="n">
         <v>-0.8325</v>
@@ -1312,13 +1312,13 @@
         <v>0.9163</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2422</v>
+        <v>-0.2474</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0717</v>
+        <v>-0.1206</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1706</v>
+        <v>-0.1267</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5785</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.389</v>
+        <v>-6.4959</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8631</v>
+        <v>-2.9453</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.5259</v>
+        <v>-3.5507</v>
       </c>
       <c r="G12" t="n">
         <v>-3.3142</v>
@@ -1390,13 +1390,13 @@
         <v>1.2828</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3493</v>
+        <v>0.2423</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0717</v>
+        <v>-0.0105</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2776</v>
+        <v>0.2528</v>
       </c>
       <c r="V12" t="n">
         <v>-3.7905</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.8622</v>
+        <v>-7.648</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.1033</v>
+        <v>-5.8148</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7589</v>
+        <v>-1.8332</v>
       </c>
       <c r="G13" t="n">
         <v>-6.566</v>
@@ -1468,13 +1468,13 @@
         <v>1.4661</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9296</v>
+        <v>-0.7155</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8997000000000001</v>
+        <v>-0.6112</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.03</v>
+        <v>-0.1043</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-41.0037</v>
+        <v>-40.453</v>
       </c>
       <c r="E14" t="n">
-        <v>-25.3407</v>
+        <v>-24.7902</v>
       </c>
       <c r="F14" t="n">
         <v>-15.663</v>
@@ -1522,10 +1522,10 @@
         <v>-6.178599999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.4109000000000003</v>
+        <v>-0.4108999999999998</v>
       </c>
       <c r="L14" t="n">
-        <v>-5.7679</v>
+        <v>-5.767900000000001</v>
       </c>
       <c r="M14" t="n">
         <v>-25.4171</v>
@@ -1537,7 +1537,7 @@
         <v>-5.7724</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9164000000000003</v>
+        <v>0.9163999999999994</v>
       </c>
       <c r="Q14" t="n">
         <v>-16.4932</v>
@@ -1546,13 +1546,13 @@
         <v>17.4096</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.3973</v>
+        <v>-2.847</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.042800000000001</v>
+        <v>-2.492</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3545</v>
+        <v>-0.3546</v>
       </c>
       <c r="V14" t="n">
         <v>-6.926600000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.379899999999999</v>
+        <v>10.0516</v>
       </c>
       <c r="E15" t="n">
-        <v>6.2815</v>
+        <v>6.0892</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0984</v>
+        <v>3.9624</v>
       </c>
       <c r="G15" t="n">
         <v>9.4145</v>
@@ -1624,13 +1624,13 @@
         <v>2.0158</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8817</v>
+        <v>1.5533</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8778</v>
+        <v>0.6855</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0038</v>
+        <v>0.8678</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.3349</v>
+        <v>6.5108</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6492</v>
+        <v>2.8415</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6858</v>
+        <v>3.6693</v>
       </c>
       <c r="G16" t="n">
         <v>4.9013</v>
@@ -1702,13 +1702,13 @@
         <v>2.3823</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2548</v>
+        <v>0.921</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1267</v>
+        <v>0.319</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3815</v>
+        <v>0.602</v>
       </c>
       <c r="V16" t="n">
         <v>0.3219</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. HOYAS PEREZ</t>
+          <t>E. CHOFRE TARREGA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.9769</v>
+        <v>5.0851</v>
       </c>
       <c r="E17" t="n">
-        <v>2.946</v>
+        <v>3.5396</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0309</v>
+        <v>1.5455</v>
       </c>
       <c r="G17" t="n">
-        <v>2.0359</v>
+        <v>4.3892</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7185</v>
+        <v>1.4338</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3174</v>
+        <v>2.9554</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8789</v>
+        <v>4.5528</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1704</v>
+        <v>1.8857</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7085</v>
+        <v>2.6672</v>
       </c>
       <c r="M17" t="n">
-        <v>0.157</v>
+        <v>-0.1636</v>
       </c>
       <c r="N17" t="n">
         <v>-0.4519</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6089</v>
+        <v>0.2882</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3665</v>
+        <v>0.1833</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9163</v>
+        <v>-1.0995</v>
       </c>
       <c r="R17" t="n">
         <v>1.2828</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3625</v>
+        <v>0.8346</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5505</v>
+        <v>0.0864</v>
       </c>
       <c r="U17" t="n">
-        <v>0.913</v>
+        <v>0.7483</v>
       </c>
       <c r="V17" t="n">
-        <v>2.212</v>
+        <v>-0.3219</v>
       </c>
       <c r="W17" t="n">
-        <v>2.5339</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>-0.3219</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. CHOFRE TARREGA</t>
+          <t>H. FABREGAT LORES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.5941</v>
+        <v>4.8506</v>
       </c>
       <c r="E18" t="n">
-        <v>3.2512</v>
+        <v>0.3766</v>
       </c>
       <c r="F18" t="n">
-        <v>1.343</v>
+        <v>4.474</v>
       </c>
       <c r="G18" t="n">
-        <v>4.3892</v>
+        <v>3.7196</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4338</v>
+        <v>3.585</v>
       </c>
       <c r="I18" t="n">
-        <v>2.9554</v>
+        <v>0.1346</v>
       </c>
       <c r="J18" t="n">
-        <v>4.5528</v>
+        <v>2.4392</v>
       </c>
       <c r="K18" t="n">
-        <v>1.8857</v>
+        <v>2.9136</v>
       </c>
       <c r="L18" t="n">
-        <v>2.6672</v>
+        <v>-0.4743</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1636</v>
+        <v>1.2804</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4519</v>
+        <v>0.6715</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2882</v>
+        <v>0.6089</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1833</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0995</v>
+        <v>-1.8326</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2828</v>
+        <v>1.4661</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3437</v>
+        <v>0.5733</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2021</v>
+        <v>-0.23</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5458</v>
+        <v>0.8033</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3219</v>
+        <v>0.9242</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3219</v>
+        <v>0.9242</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>H. FABREGAT LORES</t>
+          <t>L. RODRIGUEZ CAMPINA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4.4967</v>
+        <v>4.6538</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1843</v>
+        <v>0.3553</v>
       </c>
       <c r="F19" t="n">
-        <v>4.3123</v>
+        <v>4.2985</v>
       </c>
       <c r="G19" t="n">
-        <v>3.7196</v>
+        <v>-0.1547</v>
       </c>
       <c r="H19" t="n">
-        <v>3.585</v>
+        <v>0.5474</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1346</v>
+        <v>-0.7020999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>2.4392</v>
+        <v>-1.5387</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9136</v>
+        <v>-0.5484</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.4743</v>
+        <v>-0.9903</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2804</v>
+        <v>1.384</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6715</v>
+        <v>1.0958</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6089</v>
+        <v>0.2882</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3665</v>
+        <v>2.5656</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4661</v>
+        <v>2.5656</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2194</v>
+        <v>0.6644</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4223</v>
+        <v>-0.0064</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6417</v>
+        <v>0.6708</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9242</v>
+        <v>1.5785</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.9005</v>
       </c>
       <c r="X19" t="n">
-        <v>0.9242</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ CAMPINA</t>
+          <t>D. HOYAS PEREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>4.4031</v>
+        <v>4.5558</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8361</v>
+        <v>2.946</v>
       </c>
       <c r="F20" t="n">
-        <v>3.567</v>
+        <v>1.6097</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1547</v>
+        <v>2.0359</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5474</v>
+        <v>0.7185</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7020999999999999</v>
+        <v>1.3174</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.5387</v>
+        <v>1.8789</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5484</v>
+        <v>1.1704</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.9903</v>
+        <v>0.7085</v>
       </c>
       <c r="M20" t="n">
-        <v>1.384</v>
+        <v>0.157</v>
       </c>
       <c r="N20" t="n">
-        <v>1.0958</v>
+        <v>-0.4519</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2882</v>
+        <v>0.6089</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5656</v>
+        <v>0.3665</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5656</v>
+        <v>1.2828</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4137</v>
+        <v>-0.0586</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4744</v>
+        <v>-0.5505</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0607</v>
+        <v>0.4919</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5785</v>
+        <v>2.212</v>
       </c>
       <c r="W20" t="n">
-        <v>1.9005</v>
+        <v>2.5339</v>
       </c>
       <c r="X20" t="n">
         <v>-0.3219</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. BORISOV</t>
+          <t>J. ROIG MESA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>4.288</v>
+        <v>3.6814</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4446</v>
+        <v>1.2917</v>
       </c>
       <c r="F21" t="n">
-        <v>3.8434</v>
+        <v>2.3897</v>
       </c>
       <c r="G21" t="n">
-        <v>1.8238</v>
+        <v>2.6639</v>
       </c>
       <c r="H21" t="n">
-        <v>2.2883</v>
+        <v>2.1218</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4645</v>
+        <v>0.5421</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1693</v>
+        <v>2.2597</v>
       </c>
       <c r="K21" t="n">
-        <v>1.6656</v>
+        <v>2.8393</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.4963</v>
+        <v>-0.5797</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6545</v>
+        <v>0.4042</v>
       </c>
       <c r="N21" t="n">
-        <v>0.6226</v>
+        <v>-0.7175</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0318</v>
+        <v>1.1217</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.0995</v>
+        <v>0.733</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9321</v>
+        <v>-0.9163</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8326</v>
+        <v>1.6493</v>
       </c>
       <c r="S21" t="n">
-        <v>2.9407</v>
+        <v>0.2845</v>
       </c>
       <c r="T21" t="n">
-        <v>1.5739</v>
+        <v>-0.0516</v>
       </c>
       <c r="U21" t="n">
-        <v>1.3668</v>
+        <v>0.3361</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6231</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6335</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.0104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. ROIG MESA</t>
+          <t>D. BORISOV</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2.8495</v>
+        <v>3.4691</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8110000000000001</v>
+        <v>-0.4208</v>
       </c>
       <c r="F22" t="n">
-        <v>2.0385</v>
+        <v>3.8899</v>
       </c>
       <c r="G22" t="n">
-        <v>2.6639</v>
+        <v>1.8238</v>
       </c>
       <c r="H22" t="n">
+        <v>2.2883</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.4645</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.1693</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.6656</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-0.4963</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.6545</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.6226</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.0318</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-1.0995</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-2.9321</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.8326</v>
+      </c>
+      <c r="S22" t="n">
         <v>2.1218</v>
       </c>
-      <c r="I22" t="n">
-        <v>0.5421</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.2597</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2.8393</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-0.5797</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.4042</v>
-      </c>
-      <c r="N22" t="n">
-        <v>-0.7175</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.1217</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>-0.9163</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.6493</v>
-      </c>
-      <c r="S22" t="n">
-        <v>-0.5474</v>
-      </c>
       <c r="T22" t="n">
-        <v>-0.5324</v>
+        <v>0.7085</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.015</v>
+        <v>1.4132</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.0104</v>
       </c>
     </row>
     <row r="23">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.6745</v>
+        <v>1.8522</v>
       </c>
       <c r="E24" t="n">
         <v>1.1151</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5594</v>
+        <v>0.7372</v>
       </c>
       <c r="G24" t="n">
         <v>0.3737</v>
@@ -2326,13 +2326,13 @@
         <v>0.5498</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.516</v>
+        <v>-0.3382</v>
       </c>
       <c r="T24" t="n">
         <v>-0.3854</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1306</v>
+        <v>0.0471</v>
       </c>
       <c r="V24" t="n">
         <v>1.267</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.3252</v>
+        <v>-0.6099</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.6422</v>
+        <v>-1.2576</v>
       </c>
       <c r="F25" t="n">
-        <v>0.317</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-1.1915</v>
@@ -2404,13 +2404,13 @@
         <v>0.733</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6835</v>
+        <v>0.0319</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2202</v>
+        <v>0.1644</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4633</v>
+        <v>-0.1325</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.9195</v>
+        <v>-2.1425</v>
       </c>
       <c r="E26" t="n">
         <v>-3.4645</v>
       </c>
       <c r="F26" t="n">
-        <v>1.545</v>
+        <v>1.322</v>
       </c>
       <c r="G26" t="n">
         <v>1.3695</v>
@@ -2482,13 +2482,13 @@
         <v>0.733</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2375</v>
+        <v>0.0145</v>
       </c>
       <c r="T26" t="n">
         <v>-0.3854</v>
       </c>
       <c r="U26" t="n">
-        <v>0.6228</v>
+        <v>0.3999</v>
       </c>
       <c r="V26" t="n">
         <v>0.3219</v>
@@ -2515,16 +2515,16 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>41.0036</v>
+        <v>44.2087</v>
       </c>
       <c r="E27" t="n">
-        <v>15.663</v>
+        <v>15.6628</v>
       </c>
       <c r="F27" t="n">
-        <v>25.3407</v>
+        <v>28.5459</v>
       </c>
       <c r="G27" t="n">
-        <v>31.5959</v>
+        <v>31.59589999999999</v>
       </c>
       <c r="H27" t="n">
         <v>20.0558</v>
@@ -2551,7 +2551,7 @@
         <v>5.767499999999999</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.9161999999999999</v>
+        <v>-0.9162000000000003</v>
       </c>
       <c r="Q27" t="n">
         <v>-17.4094</v>
@@ -2560,22 +2560,22 @@
         <v>16.4931</v>
       </c>
       <c r="S27" t="n">
-        <v>3.3975</v>
+        <v>6.6025</v>
       </c>
       <c r="T27" t="n">
-        <v>0.3545000000000002</v>
+        <v>0.3545000000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>3.042800000000001</v>
+        <v>6.2479</v>
       </c>
       <c r="V27" t="n">
-        <v>6.926699999999999</v>
+        <v>6.926700000000001</v>
       </c>
       <c r="W27" t="n">
         <v>7.3007</v>
       </c>
       <c r="X27" t="n">
-        <v>-0.3737999999999999</v>
+        <v>-0.3738</v>
       </c>
     </row>
   </sheetData>
